--- a/Firmware/Modules/Imbalance/Imbalance_State_Machine.xlsx
+++ b/Firmware/Modules/Imbalance/Imbalance_State_Machine.xlsx
@@ -69,7 +69,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002F5597"/>
+        <fgColor rgb="001F4E79"/>
       </patternFill>
     </fill>
     <fill>
@@ -523,7 +523,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="002F5597"/>
+    <tabColor rgb="007F7F7F"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -680,7 +680,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="002F5597"/>
+    <tabColor rgb="007030A0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -887,7 +887,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="002F5597"/>
+    <tabColor rgb="007030A0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>

--- a/Firmware/Modules/Imbalance/Imbalance_State_Machine.xlsx
+++ b/Firmware/Modules/Imbalance/Imbalance_State_Machine.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="راهنما" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="۱ حالت‌ها" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="۲ پارامترها" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="راهنما" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="۱ حالت‌ها" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="۲ پارامترها" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
